--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV25\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5AA439-8ACE-4773-ABF9-1953BA80AE35}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A2BFED-37A6-4CF7-A5D9-1012DB9AB9F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="79">
   <si>
     <t>S.No</t>
   </si>
@@ -221,6 +221,48 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_PS_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Raw_02</t>
+  </si>
+  <si>
+    <t>Verify that stock changes are reflected and saved successfully after adjusting stock on Raw Material Section.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_04</t>
+  </si>
+  <si>
+    <t>Verify that the low stock alert is saved and reflected successfully on Raw Material Section.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Raw_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Raw_04</t>
+  </si>
+  <si>
+    <t>Verify that stock changes are reflected and saved successfully after adding stock on Raw Material Section.</t>
+  </si>
+  <si>
+    <t>Attributes</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Atbs_01</t>
+  </si>
+  <si>
+    <t>Verify admin can add a new Attributes successfully.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Atbs_01</t>
+  </si>
+  <si>
+    <t>Atrributes</t>
   </si>
 </sst>
 </file>
@@ -359,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -387,6 +429,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -394,7 +440,87 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -791,7 +917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -838,18 +964,18 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
@@ -884,43 +1010,61 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
-        <v>1</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="11">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>61</v>
+        <v>68</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>12</v>
@@ -930,29 +1074,29 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
-        <v>2</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="11">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>56</v>
+        <v>69</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>12</v>
@@ -962,41 +1106,166 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>1</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>2</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F10" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J10" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>1</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1006,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -1221,7 +1490,7 @@
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>18</v>
@@ -1304,7 +1573,7 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>18</v>
@@ -1387,7 +1656,7 @@
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>18</v>
@@ -1468,38 +1737,402 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
     </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="3"/>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="7" priority="31" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="15" priority="39" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="14" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A6">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV25\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A2BFED-37A6-4CF7-A5D9-1012DB9AB9F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AFA283-96F8-4BE7-972A-4C2D5698E623}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="85">
   <si>
     <t>S.No</t>
   </si>
@@ -263,6 +263,24 @@
   </si>
   <si>
     <t>Atrributes</t>
+  </si>
+  <si>
+    <t>Verify admin can Edit a  Attributes successfully.</t>
+  </si>
+  <si>
+    <t>Verify admin can delete Attributes successfully.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Atbs_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Atbs_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Atbs_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Atbs_03</t>
   </si>
 </sst>
 </file>
@@ -440,7 +458,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -917,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -1261,6 +1319,70 @@
         <v>13</v>
       </c>
     </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>2</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>3</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:J2"/>
@@ -1275,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -2069,70 +2191,252 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
     </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="15" priority="39" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="19" priority="43" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="18" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV25\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2new\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32AFA283-96F8-4BE7-972A-4C2D5698E623}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B98631-8363-423D-9573-7DD7397A5220}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="107">
   <si>
     <t>S.No</t>
   </si>
@@ -281,6 +281,72 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_Atbs_03</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_01</t>
+  </si>
+  <si>
+    <t>Verify that a newly created supplier is displayed on the Supplier Listing page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_02</t>
+  </si>
+  <si>
+    <t>Verify that changes made after editing a supplier are updated correctly and displayed on the Supplier Listing page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_03</t>
+  </si>
+  <si>
+    <t>Verify that contact details and bank details added from the Preview page are saved successfully</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_04</t>
+  </si>
+  <si>
+    <t>Verify that the supplier status changes to Inactive when the supplier is marked as inactive</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_05</t>
+  </si>
+  <si>
+    <t>Verify that a deleted supplier is no longer displayed on the Supplier Listing page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_06</t>
+  </si>
+  <si>
+    <t>Verify validation messages are displayed when mandatory fields are left blank while creating a supplier</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_06</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_07</t>
+  </si>
+  <si>
+    <t>Verify that multiple contact and bank account details are saved successfully while creating a new supplier</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_07</t>
   </si>
 </sst>
 </file>
@@ -419,7 +485,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -454,11 +520,172 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -975,7 +1202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -1383,11 +1610,250 @@
         <v>13</v>
       </c>
     </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <v>1</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
+        <v>2</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="14">
+        <v>3</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="14">
+        <v>4</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="14">
+        <v>5</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J20" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <v>6</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <v>7</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="J22" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A15:J15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1397,7 +1863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -2357,86 +2823,723 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
     </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="3"/>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+      <c r="U17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3"/>
+      <c r="AF17" s="3"/>
+      <c r="AG17" s="3"/>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z18" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="19" priority="43" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="35" priority="57" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="34" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="33" priority="31" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="32" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="31" priority="29" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="30" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="29" priority="27" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="28" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="27" priority="25" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="26" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="25" priority="23" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="24" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="23" priority="21" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="22" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="21" priority="19" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="20" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="17" priority="15" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2new\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV29\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B98631-8363-423D-9573-7DD7397A5220}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31CB243-A00C-439F-BA11-71D6A702C749}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="129">
   <si>
     <t>S.No</t>
   </si>
@@ -347,6 +347,72 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_SM_07</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_VM_01</t>
+  </si>
+  <si>
+    <t>Verify that a newly created vendor is displayed on the vendor Listing page.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_VM_01</t>
+  </si>
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_VM_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_VM_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_VM_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_VM_05</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_VM_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_VM_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_VM_04</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_VM_05</t>
+  </si>
+  <si>
+    <t>Verify that changes made after editing a vendor are updated correctly and displayed on the vendor Listing page.</t>
+  </si>
+  <si>
+    <t>Verify that vendor contact details and bank details added from the Preview page are saved successfully.</t>
+  </si>
+  <si>
+    <t>Verify that the vendor status changes to Inactive when the vendor is marked as inactive.</t>
+  </si>
+  <si>
+    <t>Verify that a deleted vendor is no longer displayed on the vendor Listing page.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_05</t>
+  </si>
+  <si>
+    <t>Verify admin can import Raw Material successfully.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Raw_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_06</t>
+  </si>
+  <si>
+    <t>Verify admin can Export Last 7 Days Raw Material.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_Raw_06</t>
   </si>
 </sst>
 </file>
@@ -517,15 +583,55 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="40">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1202,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -1249,18 +1355,18 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
@@ -1391,43 +1497,61 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
+      <c r="A7" s="11">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
-        <v>1</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="11">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>61</v>
+        <v>126</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>57</v>
+        <v>128</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>12</v>
@@ -1437,55 +1561,37 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
-        <v>2</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>13</v>
-      </c>
+      <c r="A9" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>11</v>
@@ -1501,43 +1607,61 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
+      <c r="A11" s="9">
+        <v>2</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>12</v>
@@ -1547,55 +1671,37 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="9">
-        <v>2</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>13</v>
-      </c>
+      <c r="A13" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>11</v>
@@ -1611,249 +1717,488 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="9">
+        <v>2</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>3</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A16" s="14">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
         <v>1</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E18" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F18" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G18" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I18" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J18" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A17" s="14">
+    <row r="19" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
         <v>2</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D19" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E19" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F19" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G19" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H19" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I19" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J19" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="14">
+    <row r="20" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
         <v>3</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D20" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E20" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F20" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G20" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H20" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I20" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J20" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14">
+    <row r="21" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
         <v>4</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E21" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F21" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G21" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H21" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I21" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J21" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14">
+    <row r="22" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="13">
         <v>5</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C22" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E22" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F22" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G22" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H22" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I22" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J22" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14">
+    <row r="23" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
         <v>6</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C23" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E23" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F23" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G23" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H23" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I23" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="J23" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="14" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14">
+    <row r="24" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
         <v>7</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C24" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D24" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F24" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G24" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H24" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I24" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="J24" s="13" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
+        <v>1</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>2</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
+        <v>3</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A29" s="13">
+        <v>4</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A30" s="13">
+        <v>5</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A25:J25"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1863,7 +2208,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG18"/>
+  <dimension ref="A1:AG25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -2327,7 +2672,7 @@
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>18</v>
@@ -2410,7 +2755,7 @@
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -2493,7 +2838,7 @@
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>18</v>
@@ -2576,7 +2921,7 @@
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>18</v>
@@ -2659,7 +3004,7 @@
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>18</v>
@@ -2742,7 +3087,7 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>18</v>
@@ -2824,8 +3169,8 @@
       <c r="AG11" s="3"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
-        <v>88</v>
+      <c r="A12" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>18</v>
@@ -2907,8 +3252,8 @@
       <c r="AG12" s="3"/>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>91</v>
+      <c r="A13" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>18</v>
@@ -2990,8 +3335,8 @@
       <c r="AG13" s="3"/>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>94</v>
+      <c r="A14" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>18</v>
@@ -3073,8 +3418,8 @@
       <c r="AG14" s="3"/>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
-        <v>97</v>
+      <c r="A15" s="13" t="s">
+        <v>91</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>18</v>
@@ -3156,8 +3501,8 @@
       <c r="AG15" s="3"/>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>100</v>
+      <c r="A16" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>18</v>
@@ -3239,8 +3584,8 @@
       <c r="AG16" s="3"/>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
-        <v>103</v>
+      <c r="A17" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>18</v>
@@ -3322,8 +3667,8 @@
       <c r="AG17" s="3"/>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>106</v>
+      <c r="A18" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>18</v>
@@ -3404,142 +3749,747 @@
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
     </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A19" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z20" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="3"/>
+      <c r="AC20" s="3"/>
+      <c r="AD20" s="3"/>
+      <c r="AE20" s="3"/>
+      <c r="AF20" s="3"/>
+      <c r="AG20" s="3"/>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+      <c r="AC21" s="3"/>
+      <c r="AD21" s="3"/>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+      <c r="AC23" s="3"/>
+      <c r="AD23" s="3"/>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="35" priority="57" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="39" priority="75" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="38" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="containsText" dxfId="37" priority="49" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="36" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="containsText" dxfId="35" priority="47" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="34" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="containsText" dxfId="33" priority="45" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="32" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="containsText" dxfId="31" priority="43" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="30" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="containsText" dxfId="29" priority="41" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="28" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5">
+    <cfRule type="containsText" dxfId="27" priority="39" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="26" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A12">
+    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="containsText" dxfId="19" priority="31" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="containsText" dxfId="15" priority="27" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A18">
+    <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A19">
+    <cfRule type="containsText" dxfId="9" priority="21" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A19)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A19)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="containsText" dxfId="7" priority="19" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A20)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:A25">
+    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A21)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="33" priority="31" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="31" priority="29" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="29" priority="27" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="27" priority="25" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="25" priority="23" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="23" priority="21" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="21" priority="19" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="19" priority="17" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="17" priority="15" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A16">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A17">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV29\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2new\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31CB243-A00C-439F-BA11-71D6A702C749}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB49758-839C-496C-91A7-0FD92E487233}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="149">
   <si>
     <t>S.No</t>
   </si>
@@ -413,6 +413,66 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_Raw_06</t>
+  </si>
+  <si>
+    <t>Purchase Order</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PO_01</t>
+  </si>
+  <si>
+    <t>Verify that a newly created Purchase Order is displayed on the Purchase Order Listing page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PO_01</t>
+  </si>
+  <si>
+    <t>PurchaseOrder</t>
+  </si>
+  <si>
+    <t>Verify that the Quantity, Price per Unit, and Total Amount are calculated and displayed correctly based on the entered quantity and price per unit</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PO_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PO_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PO_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PO_03</t>
+  </si>
+  <si>
+    <t>Verify that the edited Purchase Order details are saved successfully after editing the Purchase Order</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PO_04</t>
+  </si>
+  <si>
+    <t>Verify that after cancelling the raw material items, the Purchase Order status changes to "Cancelled" and is reflected correctly on both the Listing page and Detail page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PO_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PO_05</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PO_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PO_06</t>
+  </si>
+  <si>
+    <t>Verify that validation messages are displayed when mandatory fields are left blank and the user tries to save the Purchase Order</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PO_06</t>
+  </si>
+  <si>
+    <t>Verify that multiple raw materials can be added with available quantities and the calculated amount is displayed correctly</t>
   </si>
 </sst>
 </file>
@@ -551,7 +611,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -584,6 +644,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -591,7 +652,147 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="54">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1308,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -1355,18 +1556,18 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
@@ -1561,18 +1762,18 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
@@ -1671,18 +1872,18 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
@@ -1781,18 +1982,18 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
     </row>
     <row r="18" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
@@ -2019,18 +2220,18 @@
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
     </row>
     <row r="26" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
@@ -2192,8 +2393,215 @@
         <v>13</v>
       </c>
     </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A32" s="13">
+        <v>1</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A33" s="13">
+        <v>2</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A34" s="13">
+        <v>3</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J34" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A35" s="13">
+        <v>4</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A36" s="13">
+        <v>5</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A37" s="13">
+        <v>6</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J37" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A13:J13"/>
@@ -2208,7 +2616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG25"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -3335,7 +3743,7 @@
       <c r="AG13" s="3"/>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="14" t="s">
         <v>88</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -3418,7 +3826,7 @@
       <c r="AG14" s="3"/>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="14" t="s">
         <v>91</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -3501,7 +3909,7 @@
       <c r="AG15" s="3"/>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>94</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -3584,7 +3992,7 @@
       <c r="AG16" s="3"/>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>97</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -3667,7 +4075,7 @@
       <c r="AG17" s="3"/>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>100</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -3750,7 +4158,7 @@
       <c r="AG18" s="3"/>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>103</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -3833,7 +4241,7 @@
       <c r="AG19" s="3"/>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="14" t="s">
         <v>106</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -3916,7 +4324,7 @@
       <c r="AG20" s="3"/>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>109</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -3999,7 +4407,7 @@
       <c r="AG21" s="3"/>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="14" t="s">
         <v>115</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -4082,7 +4490,7 @@
       <c r="AG22" s="3"/>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="14" t="s">
         <v>116</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -4165,7 +4573,7 @@
       <c r="AG23" s="3"/>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="14" t="s">
         <v>117</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -4248,7 +4656,7 @@
       <c r="AG24" s="3"/>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="14" t="s">
         <v>118</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -4330,166 +4738,712 @@
       <c r="AF25" s="3"/>
       <c r="AG25" s="3"/>
     </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+      <c r="AC26" s="3"/>
+      <c r="AD26" s="3"/>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+      <c r="AC27" s="3"/>
+      <c r="AD27" s="3"/>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A28" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AD28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AD29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="3"/>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z30" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
+      <c r="AC30" s="3"/>
+      <c r="AD30" s="3"/>
+      <c r="AE30" s="3"/>
+      <c r="AF30" s="3"/>
+      <c r="AG30" s="3"/>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z31" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="3"/>
+      <c r="AC31" s="3"/>
+      <c r="AD31" s="3"/>
+      <c r="AE31" s="3"/>
+      <c r="AF31" s="3"/>
+      <c r="AG31" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="39" priority="75" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="53" priority="89" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="52" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="37" priority="49" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="51" priority="63" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="50" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="35" priority="47" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="49" priority="61" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="48" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="33" priority="45" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="47" priority="59" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="46" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="31" priority="43" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="45" priority="57" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="44" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="29" priority="41" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="43" priority="55" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="42" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="27" priority="39" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="41" priority="53" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="40" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="39" priority="51" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="38" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="37" priority="49" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="36" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="35" priority="47" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="34" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="containsText" dxfId="19" priority="31" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="33" priority="45" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="32" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="31" priority="43" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="30" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="containsText" dxfId="15" priority="27" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="29" priority="41" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="28" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="27" priority="39" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="26" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="24" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="containsText" dxfId="9" priority="21" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="containsText" dxfId="7" priority="19" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="20" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A25">
-    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="19" priority="31" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="18" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A26)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A26)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A27)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A28">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A28)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A28)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A29)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A29)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A30)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A30)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A31">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A31)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2new\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV233\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB49758-839C-496C-91A7-0FD92E487233}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F710F0DC-FDD2-48FB-A35F-0BC37C1FFA2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="170">
   <si>
     <t>S.No</t>
   </si>
@@ -473,6 +473,69 @@
   </si>
   <si>
     <t>Verify that multiple raw materials can be added with available quantities and the calculated amount is displayed correctly</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PR_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PR_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PR_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PR_02</t>
+  </si>
+  <si>
+    <t>Verify that a newly created Purchase Receive In Transit Status is displayed on the Purchase Receive Listing page</t>
+  </si>
+  <si>
+    <t>Verify Purchase Receive the Received Status is displayed correctly on Listing and Preview Page.</t>
+  </si>
+  <si>
+    <t>Verify that the convert bill option should redirect to bill module.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PR_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PR_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PR_04</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PR_04</t>
+  </si>
+  <si>
+    <t>Verify that validation messages are displayed when mandatory fields are left blank and the user tries to save the Purchase Receive</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_WH_01</t>
+  </si>
+  <si>
+    <t>Verify that a newly created WareHouse  is displayed on the WareHouse Listing page.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_WH_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_WH_02</t>
+  </si>
+  <si>
+    <t>Verify that changes made after editing a WareHouse are updated correctly and displayed on the WareHouse Listing page.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_WH_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_WH_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_WH_03</t>
+  </si>
+  <si>
+    <t>Verify that Set as main Branch functionalty.</t>
   </si>
 </sst>
 </file>
@@ -652,7 +715,127 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="54">
+  <dxfs count="66">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1509,7 +1692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -2599,8 +2782,262 @@
         <v>13</v>
       </c>
     </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+    </row>
+    <row r="39" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
+        <v>1</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H39" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A40" s="13">
+        <v>2</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I40" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
+        <v>3</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A42" s="13">
+        <v>4</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A44" s="13">
+        <v>1</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A45" s="13">
+        <v>2</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A46" s="13">
+        <v>3</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H46" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I46" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A9:J9"/>
@@ -2616,7 +3053,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG31"/>
+  <dimension ref="A1:AG38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -5236,214 +5673,851 @@
       <c r="AF31" s="3"/>
       <c r="AG31" s="3"/>
     </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A32" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z32" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="3"/>
+      <c r="AC32" s="3"/>
+      <c r="AD32" s="3"/>
+      <c r="AE32" s="3"/>
+      <c r="AF32" s="3"/>
+      <c r="AG32" s="3"/>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="3"/>
+      <c r="AC33" s="3"/>
+      <c r="AD33" s="3"/>
+      <c r="AE33" s="3"/>
+      <c r="AF33" s="3"/>
+      <c r="AG33" s="3"/>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S34" s="3"/>
+      <c r="T34" s="3"/>
+      <c r="U34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z34" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="3"/>
+      <c r="AC34" s="3"/>
+      <c r="AD34" s="3"/>
+      <c r="AE34" s="3"/>
+      <c r="AF34" s="3"/>
+      <c r="AG34" s="3"/>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A35" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S35" s="3"/>
+      <c r="T35" s="3"/>
+      <c r="U35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z35" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA35" s="3"/>
+      <c r="AB35" s="3"/>
+      <c r="AC35" s="3"/>
+      <c r="AD35" s="3"/>
+      <c r="AE35" s="3"/>
+      <c r="AF35" s="3"/>
+      <c r="AG35" s="3"/>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A36" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S36" s="3"/>
+      <c r="T36" s="3"/>
+      <c r="U36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z36" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="3"/>
+      <c r="AC36" s="3"/>
+      <c r="AD36" s="3"/>
+      <c r="AE36" s="3"/>
+      <c r="AF36" s="3"/>
+      <c r="AG36" s="3"/>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S37" s="3"/>
+      <c r="T37" s="3"/>
+      <c r="U37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z37" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="3"/>
+      <c r="AC37" s="3"/>
+      <c r="AD37" s="3"/>
+      <c r="AE37" s="3"/>
+      <c r="AF37" s="3"/>
+      <c r="AG37" s="3"/>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S38" s="3"/>
+      <c r="T38" s="3"/>
+      <c r="U38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z38" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="3"/>
+      <c r="AC38" s="3"/>
+      <c r="AD38" s="3"/>
+      <c r="AE38" s="3"/>
+      <c r="AF38" s="3"/>
+      <c r="AG38" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="53" priority="89" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="65" priority="103" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="64" priority="104" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="51" priority="63" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="63" priority="77" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="62" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="49" priority="61" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="61" priority="75" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="60" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="47" priority="59" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="59" priority="73" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="58" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="45" priority="57" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="57" priority="71" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="56" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="43" priority="55" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="55" priority="69" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="54" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="41" priority="53" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="53" priority="67" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="52" priority="68" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="39" priority="51" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="51" priority="65" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="50" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="37" priority="49" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="49" priority="63" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="48" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="containsText" dxfId="35" priority="47" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="47" priority="61" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="46" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="containsText" dxfId="33" priority="45" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="45" priority="59" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="44" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="containsText" dxfId="31" priority="43" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="43" priority="57" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="42" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="containsText" dxfId="29" priority="41" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="41" priority="55" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="40" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="containsText" dxfId="27" priority="39" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="39" priority="53" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="38" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="37" priority="51" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="36" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="35" priority="49" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="34" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="33" priority="47" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="32" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A25">
-    <cfRule type="containsText" dxfId="19" priority="31" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="31" priority="45" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="30" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="28" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="27" priority="29" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="26" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="25" priority="27" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A26)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="24" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="23" priority="25" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A27)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="22" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A28)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A28)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="19" priority="21" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A29)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="18" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A31)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A31)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A32">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A32)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A32)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A33">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A33)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A33)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A34">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A34)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A34)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A35)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A35)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A36">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A36)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A36)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A37">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A37)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A31)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A37)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A38">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A38)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV233\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2Remote\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F710F0DC-FDD2-48FB-A35F-0BC37C1FFA2F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A07458E-0DDC-457C-BC96-D502E4BB58B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1272" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="194">
   <si>
     <t>S.No</t>
   </si>
@@ -536,6 +536,78 @@
   </si>
   <si>
     <t>Verify that Set as main Branch functionalty.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MO_01</t>
+  </si>
+  <si>
+    <t>Verify that a newly created Manufacture Order is displayed on the Manufacture Order Listing page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MO_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MO_02</t>
+  </si>
+  <si>
+    <t>Verify that when a product is saved as Draft, the status is displayed as Draft and the Draft product can be deleted</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MO_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MO_03</t>
+  </si>
+  <si>
+    <t>Verify that the user is able to edit the Manufacture Order and the edited Manufacture Order details are reflected correctly</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MO_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MO_04</t>
+  </si>
+  <si>
+    <t>Verify that the "Cancel Items" option is available and that the order status changes to "Cancelled" after cancelling the items</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MO_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MO_05</t>
+  </si>
+  <si>
+    <t>Verify that when an Open Manufacture Order is marked as Issued, the status is changed to Issued on both the Listing page and Detail page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MO_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MO_06</t>
+  </si>
+  <si>
+    <t>Verify that when the user tries to save a Manufacture Order without entering the mandatory details, the mandatory field validation messages are displayed</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MO_06</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MO_07</t>
+  </si>
+  <si>
+    <t>Verify that multiple products and raw materials can be added while creating a new Manufacture Order</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MO_07</t>
+  </si>
+  <si>
+    <t>Manufacture Order</t>
+  </si>
+  <si>
+    <t>Warehouse</t>
+  </si>
+  <si>
+    <t>Purchase Receive</t>
   </si>
 </sst>
 </file>
@@ -715,7 +787,147 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="66">
+  <dxfs count="80">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1692,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -2784,7 +2996,7 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="15" t="s">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="B38" s="15"/>
       <c r="C38" s="15"/>
@@ -2926,7 +3138,7 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="B43" s="15"/>
       <c r="C43" s="15"/>
@@ -3034,8 +3246,247 @@
         <v>13</v>
       </c>
     </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>1</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>170</v>
+      </c>
+      <c r="D48" t="s">
+        <v>171</v>
+      </c>
+      <c r="E48" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" t="s">
+        <v>172</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" t="s">
+        <v>133</v>
+      </c>
+      <c r="I48" t="s">
+        <v>12</v>
+      </c>
+      <c r="J48" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>2</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>173</v>
+      </c>
+      <c r="D49" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
+        <v>175</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" t="s">
+        <v>176</v>
+      </c>
+      <c r="D50" t="s">
+        <v>174</v>
+      </c>
+      <c r="E50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" t="s">
+        <v>178</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>4</v>
+      </c>
+      <c r="B51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" t="s">
+        <v>179</v>
+      </c>
+      <c r="D51" t="s">
+        <v>180</v>
+      </c>
+      <c r="E51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F51" t="s">
+        <v>181</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" t="s">
+        <v>133</v>
+      </c>
+      <c r="I51" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" t="s">
+        <v>183</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" t="s">
+        <v>184</v>
+      </c>
+      <c r="G52" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" t="s">
+        <v>133</v>
+      </c>
+      <c r="I52" t="s">
+        <v>12</v>
+      </c>
+      <c r="J52" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" t="s">
+        <v>185</v>
+      </c>
+      <c r="D53" t="s">
+        <v>186</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s">
+        <v>187</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" t="s">
+        <v>133</v>
+      </c>
+      <c r="I53" t="s">
+        <v>12</v>
+      </c>
+      <c r="J53" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s">
+        <v>188</v>
+      </c>
+      <c r="D54" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s">
+        <v>190</v>
+      </c>
+      <c r="G54" t="s">
+        <v>11</v>
+      </c>
+      <c r="H54" t="s">
+        <v>133</v>
+      </c>
+      <c r="I54" t="s">
+        <v>12</v>
+      </c>
+      <c r="J54" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A47:J47"/>
     <mergeCell ref="A43:J43"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A31:J31"/>
@@ -3053,7 +3504,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG38"/>
+  <dimension ref="A1:AG45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -6254,270 +6705,859 @@
       <c r="AF38" s="3"/>
       <c r="AG38" s="3"/>
     </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A39" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+      <c r="U39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z39" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A40" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z40" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z41" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="3"/>
+      <c r="AD41" s="3"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="3"/>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A42" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z42" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA42" s="3"/>
+      <c r="AB42" s="3"/>
+      <c r="AC42" s="3"/>
+      <c r="AD42" s="3"/>
+      <c r="AE42" s="3"/>
+      <c r="AF42" s="3"/>
+      <c r="AG42" s="3"/>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S43" s="3"/>
+      <c r="T43" s="3"/>
+      <c r="U43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z43" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA43" s="3"/>
+      <c r="AB43" s="3"/>
+      <c r="AC43" s="3"/>
+      <c r="AD43" s="3"/>
+      <c r="AE43" s="3"/>
+      <c r="AF43" s="3"/>
+      <c r="AG43" s="3"/>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A44" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S44" s="3"/>
+      <c r="T44" s="3"/>
+      <c r="U44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z44" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA44" s="3"/>
+      <c r="AB44" s="3"/>
+      <c r="AC44" s="3"/>
+      <c r="AD44" s="3"/>
+      <c r="AE44" s="3"/>
+      <c r="AF44" s="3"/>
+      <c r="AG44" s="3"/>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S45" s="3"/>
+      <c r="T45" s="3"/>
+      <c r="U45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA45" s="3"/>
+      <c r="AB45" s="3"/>
+      <c r="AC45" s="3"/>
+      <c r="AD45" s="3"/>
+      <c r="AE45" s="3"/>
+      <c r="AF45" s="3"/>
+      <c r="AG45" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="65" priority="103" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="79" priority="117" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="104" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="78" priority="118" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="63" priority="77" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="77" priority="91" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="76" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="61" priority="75" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="75" priority="89" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="74" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="59" priority="73" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="73" priority="87" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="72" priority="88" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="57" priority="71" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="71" priority="85" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="70" priority="86" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="55" priority="69" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="69" priority="83" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="68" priority="84" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="53" priority="67" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="67" priority="81" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="68" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="66" priority="82" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="51" priority="65" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="65" priority="79" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="64" priority="80" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="49" priority="63" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="63" priority="77" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="62" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="containsText" dxfId="47" priority="61" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="61" priority="75" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="60" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="containsText" dxfId="45" priority="59" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="59" priority="73" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="58" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="containsText" dxfId="43" priority="57" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="57" priority="71" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="56" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="containsText" dxfId="41" priority="55" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="55" priority="69" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="54" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="containsText" dxfId="39" priority="53" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="53" priority="67" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="52" priority="68" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="containsText" dxfId="37" priority="51" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="51" priority="65" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="50" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="containsText" dxfId="35" priority="49" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="49" priority="63" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="48" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="containsText" dxfId="33" priority="47" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="47" priority="61" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="46" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A25">
-    <cfRule type="containsText" dxfId="31" priority="45" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="45" priority="59" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="44" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="43" priority="45" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="42" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="27" priority="29" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="41" priority="43" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="40" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26">
-    <cfRule type="containsText" dxfId="25" priority="27" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="39" priority="41" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A26)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="38" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="containsText" dxfId="23" priority="25" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A27)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="36" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A28)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="34" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A28)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29">
-    <cfRule type="containsText" dxfId="19" priority="21" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="33" priority="35" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A29)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="32" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30">
-    <cfRule type="containsText" dxfId="17" priority="19" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="31" priority="33" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="30" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31">
-    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="28" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A32)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A32)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A33)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A36)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A36)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A37)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A38)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A38)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A39:A45">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A39)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2Remote\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV266\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A07458E-0DDC-457C-BC96-D502E4BB58B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F6AE0F-555C-4445-B25D-33A208D18110}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="211">
   <si>
     <t>S.No</t>
   </si>
@@ -608,6 +608,57 @@
   </si>
   <si>
     <t>Purchase Receive</t>
+  </si>
+  <si>
+    <t>Manufacture Receive</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MR_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MR_01</t>
+  </si>
+  <si>
+    <t>Verify that a newly created Manufacture Receive In Transit Status is displayed on the Manufacture Receive Listing page</t>
+  </si>
+  <si>
+    <t>ManufactureOrder</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MR_02</t>
+  </si>
+  <si>
+    <t>Verify Manufacture Receive the Received Status is displayed correctly on Listing and Preview Page.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MR_02</t>
+  </si>
+  <si>
+    <t>Verify that validation messages are displayed when mandatory fields are left blank on create page and the user tries to save the Manufacture Receive</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MR_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MR_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MR_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MR_04</t>
+  </si>
+  <si>
+    <t>Verify that validation messages are displayed when mandatory fields are left blank and the user tries to save the Manufacture Receive</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MR_05</t>
+  </si>
+  <si>
+    <t>Verify admin can delete Manufacture Receive successfully.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MR_05</t>
   </si>
 </sst>
 </file>
@@ -787,27 +838,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="80">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="78">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1904,7 +1935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -3484,17 +3515,192 @@
         <v>13</v>
       </c>
     </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+    </row>
+    <row r="56" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A56" s="13">
+        <v>1</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="I56" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A57" s="13">
+        <v>2</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A58" s="13">
+        <v>3</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E58" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H58" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="I58" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A59" s="13">
+        <v>4</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="I59" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A60" s="13">
+        <v>5</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="I60" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J60" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A31:J31"/>
+  <mergeCells count="10">
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A9:J9"/>
     <mergeCell ref="A13:J13"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A31:J31"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3504,7 +3710,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG45"/>
+  <dimension ref="A1:AG50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -7286,278 +7492,733 @@
       <c r="AF45" s="3"/>
       <c r="AG45" s="3"/>
     </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A46" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S46" s="3"/>
+      <c r="T46" s="3"/>
+      <c r="U46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z46" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="3"/>
+      <c r="AC46" s="3"/>
+      <c r="AD46" s="3"/>
+      <c r="AE46" s="3"/>
+      <c r="AF46" s="3"/>
+      <c r="AG46" s="3"/>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A47" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S47" s="3"/>
+      <c r="T47" s="3"/>
+      <c r="U47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z47" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA47" s="3"/>
+      <c r="AB47" s="3"/>
+      <c r="AC47" s="3"/>
+      <c r="AD47" s="3"/>
+      <c r="AE47" s="3"/>
+      <c r="AF47" s="3"/>
+      <c r="AG47" s="3"/>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A48" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z48" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA48" s="3"/>
+      <c r="AB48" s="3"/>
+      <c r="AC48" s="3"/>
+      <c r="AD48" s="3"/>
+      <c r="AE48" s="3"/>
+      <c r="AF48" s="3"/>
+      <c r="AG48" s="3"/>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A49" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S49" s="3"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z49" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA49" s="3"/>
+      <c r="AB49" s="3"/>
+      <c r="AC49" s="3"/>
+      <c r="AD49" s="3"/>
+      <c r="AE49" s="3"/>
+      <c r="AF49" s="3"/>
+      <c r="AG49" s="3"/>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A50" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S50" s="3"/>
+      <c r="T50" s="3"/>
+      <c r="U50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA50" s="3"/>
+      <c r="AB50" s="3"/>
+      <c r="AC50" s="3"/>
+      <c r="AD50" s="3"/>
+      <c r="AE50" s="3"/>
+      <c r="AF50" s="3"/>
+      <c r="AG50" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="79" priority="117" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="77" priority="127" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="118" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="76" priority="128" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="77" priority="91" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="75" priority="101" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="74" priority="102" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="75" priority="89" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="73" priority="99" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="72" priority="100" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="73" priority="87" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="71" priority="97" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="88" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="70" priority="98" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="71" priority="85" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="69" priority="95" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="86" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="68" priority="96" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="69" priority="83" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="67" priority="93" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="84" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="66" priority="94" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="67" priority="81" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="65" priority="91" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="82" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="64" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="65" priority="79" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="63" priority="89" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="80" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="62" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="63" priority="77" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="61" priority="87" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="60" priority="88" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="containsText" dxfId="61" priority="75" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="59" priority="85" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="58" priority="86" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="containsText" dxfId="59" priority="73" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="57" priority="83" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="56" priority="84" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="containsText" dxfId="57" priority="71" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="55" priority="81" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="54" priority="82" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="containsText" dxfId="55" priority="69" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="53" priority="79" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="52" priority="80" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="containsText" dxfId="53" priority="67" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="51" priority="77" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="68" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="50" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="containsText" dxfId="51" priority="65" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="49" priority="75" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="48" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="containsText" dxfId="49" priority="63" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="47" priority="73" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="46" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="containsText" dxfId="47" priority="61" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="45" priority="71" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="44" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21:A25">
-    <cfRule type="containsText" dxfId="45" priority="59" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="43" priority="69" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="42" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="43" priority="45" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="41" priority="55" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="40" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="41" priority="43" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="39" priority="53" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="38" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A26">
-    <cfRule type="containsText" dxfId="39" priority="41" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="37" priority="51" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A26)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="36" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A26)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A27">
-    <cfRule type="containsText" dxfId="37" priority="39" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="35" priority="49" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A27)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="34" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A27)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28">
-    <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="33" priority="47" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A28)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="32" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A28)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29">
-    <cfRule type="containsText" dxfId="33" priority="35" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="31" priority="45" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A29)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="30" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30">
-    <cfRule type="containsText" dxfId="31" priority="33" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="29" priority="43" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="28" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31">
-    <cfRule type="containsText" dxfId="29" priority="31" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="27" priority="41" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="26" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32">
-    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A32)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="24" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A32)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33">
-    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A33)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
-    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="20" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35">
-    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="19" priority="31" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="18" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36">
-    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A36)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="16" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A36)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="15" priority="27" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="14" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A37)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A38)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="12" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39:A45">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="10" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A39)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A46)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A46)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A47">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A47)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A47)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A48">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A48)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A48)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A49">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A49)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A49)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A50">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A50)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A50)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV266\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2Remote\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F6AE0F-555C-4445-B25D-33A208D18110}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F3D7FE-411D-452D-86BD-1804BA734F74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="226">
   <si>
     <t>S.No</t>
   </si>
@@ -659,13 +659,58 @@
   </si>
   <si>
     <t>TD_UI_Zlaata_MR_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_MO_08</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_MO_08</t>
+  </si>
+  <si>
+    <t>Verify that the Manufacture Order export functionality works correctly and the corresponding columns are exported accurately in the Excel file</t>
+  </si>
+  <si>
+    <t>Verify that the Purchase Order export functionality works correctly and the corresponding columns are exported accurately in the Excel file</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PO_07</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PO_07</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PS_04</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PS_04</t>
+  </si>
+  <si>
+    <t>Verify that the Product Stocks export functionality works correctly and the corresponding columns are exported accurately in the Excel file</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_08</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_08</t>
+  </si>
+  <si>
+    <t>Verify that the supplier export functionality works correctly and the corresponding columns are exported accurately in the Excel file</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SM_09</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SM_09</t>
+  </si>
+  <si>
+    <t>Verify that the supplier import functionality works correctly and valid supplier data is imported successfully</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -712,6 +757,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -797,7 +848,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -831,6 +882,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -838,7 +890,107 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="78">
+  <dxfs count="88">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1935,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -1982,18 +2134,18 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
@@ -2188,18 +2340,18 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
@@ -2298,69 +2450,69 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="9">
+        <v>4</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
-        <v>1</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>13</v>
-      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>11</v>
@@ -2377,22 +2529,22 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>11</v>
@@ -2408,69 +2560,69 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="9">
+        <v>3</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-    </row>
-    <row r="18" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
-        <v>1</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>13</v>
-      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
     </row>
     <row r="19" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G19" s="13" t="s">
         <v>11</v>
@@ -2487,22 +2639,22 @@
     </row>
     <row r="20" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>11</v>
@@ -2519,22 +2671,22 @@
     </row>
     <row r="21" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>11</v>
@@ -2551,22 +2703,22 @@
     </row>
     <row r="22" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>11</v>
@@ -2583,22 +2735,22 @@
     </row>
     <row r="23" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>11</v>
@@ -2615,22 +2767,22 @@
     </row>
     <row r="24" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>11</v>
@@ -2645,44 +2797,62 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
+    <row r="25" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A25" s="13">
+        <v>7</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="26" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>107</v>
+        <v>220</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>108</v>
+        <v>222</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>109</v>
+        <v>221</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
         <v>12</v>
@@ -2693,28 +2863,28 @@
     </row>
     <row r="27" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>111</v>
+        <v>223</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>119</v>
+        <v>225</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>115</v>
+        <v>224</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>12</v>
@@ -2723,56 +2893,38 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A28" s="13">
-        <v>3</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H28" s="13" t="s">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="I28" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>13</v>
-      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
     </row>
     <row r="29" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>11</v>
@@ -2789,22 +2941,22 @@
     </row>
     <row r="30" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>11</v>
@@ -2819,44 +2971,62 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
+    <row r="31" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A31" s="13">
+        <v>3</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="32" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E32" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="I32" s="13" t="s">
         <v>12</v>
@@ -2867,28 +3037,28 @@
     </row>
     <row r="33" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E33" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>12</v>
@@ -2897,56 +3067,38 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A34" s="13">
-        <v>3</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D34" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>13</v>
-      </c>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A35" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>11</v>
@@ -2963,22 +3115,22 @@
     </row>
     <row r="36" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>11</v>
@@ -2995,22 +3147,22 @@
     </row>
     <row r="37" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A37" s="13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E37" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>11</v>
@@ -3025,38 +3177,56 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
+    <row r="38" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="13">
+        <v>4</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H38" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="39" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>11</v>
@@ -3073,22 +3243,22 @@
     </row>
     <row r="40" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E40" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>11</v>
@@ -3105,22 +3275,22 @@
     </row>
     <row r="41" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A41" s="13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>11</v>
@@ -3135,70 +3305,70 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A42" s="13">
-        <v>4</v>
-      </c>
-      <c r="B42" s="13" t="s">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+    </row>
+    <row r="43" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="13">
+        <v>1</v>
+      </c>
+      <c r="B43" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" s="13" t="s">
+      <c r="C43" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F42" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="G42" s="13" t="s">
+      <c r="F43" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="G43" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H42" s="13" t="s">
+      <c r="H43" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="I42" s="13" t="s">
+      <c r="I43" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J42" s="13" t="s">
+      <c r="J43" s="13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
-        <v>192</v>
-      </c>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
     </row>
     <row r="44" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E44" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>11</v>
@@ -3215,22 +3385,22 @@
     </row>
     <row r="45" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A45" s="13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="G45" s="13" t="s">
         <v>11</v>
@@ -3247,22 +3417,22 @@
     </row>
     <row r="46" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A46" s="13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="E46" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>11</v>
@@ -3278,429 +3448,571 @@
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B47" s="16"/>
+      <c r="C47" s="16"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="16"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+    </row>
+    <row r="48" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A48" s="13">
+        <v>1</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J48" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A49" s="13">
+        <v>2</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H49" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I49" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A50" s="13">
+        <v>3</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H50" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I50" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48">
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+    </row>
+    <row r="52" spans="1:10" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
         <v>1</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B52" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C52" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D52" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E52" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F52" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G52" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H52" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I52" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J52" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49">
+    <row r="53" spans="1:10" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A53" s="15">
         <v>2</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B53" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C53" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D53" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E53" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F53" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="G49" t="s">
+      <c r="G53" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H53" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I49" t="s">
+      <c r="I53" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J49" t="s">
+      <c r="J53" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50">
+    <row r="54" spans="1:10" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
         <v>3</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B54" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C54" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D54" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E54" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F54" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="G50" t="s">
+      <c r="G54" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H54" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I50" t="s">
+      <c r="I54" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J54" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51">
+    <row r="55" spans="1:10" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A55" s="15">
         <v>4</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B55" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C55" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D55" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E55" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F55" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="G51" t="s">
+      <c r="G55" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H55" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I51" t="s">
+      <c r="I55" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J51" t="s">
+      <c r="J55" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52">
+    <row r="56" spans="1:10" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A56" s="15">
         <v>5</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B56" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C56" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D56" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E56" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F56" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="G52" t="s">
+      <c r="G56" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H56" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I52" t="s">
+      <c r="I56" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J52" t="s">
+      <c r="J56" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53">
+    <row r="57" spans="1:10" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A57" s="15">
         <v>6</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B57" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C57" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D57" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E57" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F57" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="G53" t="s">
+      <c r="G57" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H57" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I53" t="s">
+      <c r="I57" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J53" t="s">
+      <c r="J57" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54">
+    <row r="58" spans="1:10" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A58" s="15">
         <v>7</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B58" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C58" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D58" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E58" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F58" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="G54" t="s">
+      <c r="G58" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H58" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I54" t="s">
+      <c r="I58" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="J54" t="s">
+      <c r="J58" s="15" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="15" t="s">
+    <row r="59" spans="1:10" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A59" s="15">
+        <v>8</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="E59" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="G59" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="I59" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J59" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
-    </row>
-    <row r="56" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A56" s="13">
+      <c r="B60" s="16"/>
+      <c r="C60" s="16"/>
+      <c r="D60" s="16"/>
+      <c r="E60" s="16"/>
+      <c r="F60" s="16"/>
+      <c r="G60" s="16"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+    </row>
+    <row r="61" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A61" s="13">
         <v>1</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B61" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C56" s="13" t="s">
+      <c r="C61" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="D56" s="13" t="s">
+      <c r="D61" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E56" s="13" t="s">
+      <c r="E61" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F56" s="13" t="s">
+      <c r="F61" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="G56" s="13" t="s">
+      <c r="G61" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H56" s="13" t="s">
+      <c r="H61" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="I56" s="13" t="s">
+      <c r="I61" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J56" s="13" t="s">
+      <c r="J61" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A57" s="13">
+    <row r="62" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A62" s="13">
         <v>2</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B62" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C62" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D62" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="E57" s="13" t="s">
+      <c r="E62" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F57" s="13" t="s">
+      <c r="F62" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="G57" s="13" t="s">
+      <c r="G62" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H57" s="13" t="s">
+      <c r="H62" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="I57" s="13" t="s">
+      <c r="I62" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J57" s="13" t="s">
+      <c r="J62" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A58" s="13">
+    <row r="63" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A63" s="13">
         <v>3</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B63" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C63" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D63" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="E58" s="13" t="s">
+      <c r="E63" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F58" s="13" t="s">
+      <c r="F63" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="G58" s="13" t="s">
+      <c r="G63" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H58" s="13" t="s">
+      <c r="H63" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="I58" s="13" t="s">
+      <c r="I63" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J58" s="13" t="s">
+      <c r="J63" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A59" s="13">
+    <row r="64" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A64" s="13">
         <v>4</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B64" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C64" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D64" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="E59" s="13" t="s">
+      <c r="E64" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F59" s="13" t="s">
+      <c r="F64" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="G59" s="13" t="s">
+      <c r="G64" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H59" s="13" t="s">
+      <c r="H64" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="I59" s="13" t="s">
+      <c r="I64" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J59" s="13" t="s">
+      <c r="J64" s="13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A60" s="13">
+    <row r="65" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A65" s="13">
         <v>5</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B65" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C65" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D65" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="E60" s="13" t="s">
+      <c r="E65" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F60" s="13" t="s">
+      <c r="F65" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="G60" s="13" t="s">
+      <c r="G65" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H60" s="13" t="s">
+      <c r="H65" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="I60" s="13" t="s">
+      <c r="I65" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="J60" s="13" t="s">
+      <c r="J65" s="13" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A34:J34"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A28:J28"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3710,7 +4022,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG50"/>
+  <dimension ref="A1:AG55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -4589,7 +4901,7 @@
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>18</v>
@@ -4672,7 +4984,7 @@
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>18</v>
@@ -4755,7 +5067,7 @@
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>18</v>
@@ -4837,8 +5149,8 @@
       <c r="AG13" s="3"/>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>88</v>
+      <c r="A14" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>18</v>
@@ -4921,7 +5233,7 @@
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>18</v>
@@ -5004,7 +5316,7 @@
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>18</v>
@@ -5087,7 +5399,7 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>18</v>
@@ -5170,7 +5482,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>18</v>
@@ -5253,7 +5565,7 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>18</v>
@@ -5336,7 +5648,7 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>18</v>
@@ -5419,7 +5731,7 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>18</v>
@@ -5502,7 +5814,7 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>18</v>
@@ -5585,7 +5897,7 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
-        <v>116</v>
+        <v>224</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>18</v>
@@ -5668,7 +5980,7 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>18</v>
@@ -5751,7 +6063,7 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>18</v>
@@ -5834,7 +6146,7 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>18</v>
@@ -5917,7 +6229,7 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>18</v>
@@ -6000,7 +6312,7 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>18</v>
@@ -6083,7 +6395,7 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>18</v>
@@ -6166,7 +6478,7 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>18</v>
@@ -6249,7 +6561,7 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>18</v>
@@ -6332,7 +6644,7 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>18</v>
@@ -6415,7 +6727,7 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>18</v>
@@ -6498,7 +6810,7 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>18</v>
@@ -6581,7 +6893,7 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>18</v>
@@ -6664,7 +6976,7 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>18</v>
@@ -6747,7 +7059,7 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>18</v>
@@ -6830,7 +7142,7 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>18</v>
@@ -6913,7 +7225,7 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>18</v>
@@ -6996,7 +7308,7 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>18</v>
@@ -7079,7 +7391,7 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>18</v>
@@ -7162,7 +7474,7 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>18</v>
@@ -7245,7 +7557,7 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>18</v>
@@ -7328,7 +7640,7 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>18</v>
@@ -7411,7 +7723,7 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>18</v>
@@ -7494,7 +7806,7 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>18</v>
@@ -7577,7 +7889,7 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>18</v>
@@ -7660,7 +7972,7 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>18</v>
@@ -7743,7 +8055,7 @@
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>18</v>
@@ -7826,7 +8138,7 @@
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>18</v>
@@ -7907,318 +8219,773 @@
       <c r="AF50" s="3"/>
       <c r="AG50" s="3"/>
     </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A51" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S51" s="3"/>
+      <c r="T51" s="3"/>
+      <c r="U51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z51" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA51" s="3"/>
+      <c r="AB51" s="3"/>
+      <c r="AC51" s="3"/>
+      <c r="AD51" s="3"/>
+      <c r="AE51" s="3"/>
+      <c r="AF51" s="3"/>
+      <c r="AG51" s="3"/>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A52" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S52" s="3"/>
+      <c r="T52" s="3"/>
+      <c r="U52" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y52" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z52" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA52" s="3"/>
+      <c r="AB52" s="3"/>
+      <c r="AC52" s="3"/>
+      <c r="AD52" s="3"/>
+      <c r="AE52" s="3"/>
+      <c r="AF52" s="3"/>
+      <c r="AG52" s="3"/>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A53" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S53" s="3"/>
+      <c r="T53" s="3"/>
+      <c r="U53" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y53" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z53" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA53" s="3"/>
+      <c r="AB53" s="3"/>
+      <c r="AC53" s="3"/>
+      <c r="AD53" s="3"/>
+      <c r="AE53" s="3"/>
+      <c r="AF53" s="3"/>
+      <c r="AG53" s="3"/>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A54" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S54" s="3"/>
+      <c r="T54" s="3"/>
+      <c r="U54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z54" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA54" s="3"/>
+      <c r="AB54" s="3"/>
+      <c r="AC54" s="3"/>
+      <c r="AD54" s="3"/>
+      <c r="AE54" s="3"/>
+      <c r="AF54" s="3"/>
+      <c r="AG54" s="3"/>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A55" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y55" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z55" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="77" priority="127" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="87" priority="137" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="128" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="86" priority="138" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="75" priority="101" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="85" priority="111" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="102" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="84" priority="112" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="73" priority="99" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="83" priority="109" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="100" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="82" priority="110" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="71" priority="97" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="81" priority="107" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="98" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="80" priority="108" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="69" priority="95" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="79" priority="105" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="96" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="78" priority="106" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="67" priority="93" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="77" priority="103" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="94" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="76" priority="104" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="65" priority="91" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="75" priority="101" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="74" priority="102" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="63" priority="89" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="61" priority="87" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="73" priority="99" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="88" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="72" priority="100" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="containsText" dxfId="59" priority="85" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="71" priority="97" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="86" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="70" priority="98" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="containsText" dxfId="57" priority="83" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="69" priority="95" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="84" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="68" priority="96" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="containsText" dxfId="55" priority="81" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="67" priority="93" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="82" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="66" priority="94" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="containsText" dxfId="53" priority="79" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="65" priority="91" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="80" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="64" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="containsText" dxfId="51" priority="77" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="63" priority="89" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="62" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="containsText" dxfId="49" priority="75" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="61" priority="87" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="60" priority="88" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="containsText" dxfId="47" priority="73" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="59" priority="85" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="58" priority="86" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="containsText" dxfId="45" priority="71" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="57" priority="83" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="56" priority="84" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A20)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A21:A25">
-    <cfRule type="containsText" dxfId="43" priority="69" operator="containsText" text="&lt;NA&gt;">
+  <conditionalFormatting sqref="A21">
+    <cfRule type="containsText" dxfId="55" priority="81" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="54" priority="82" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A21)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A24:A28">
+    <cfRule type="containsText" dxfId="53" priority="79" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A24)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="52" priority="80" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="41" priority="55" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="51" priority="65" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="50" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="39" priority="53" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="49" priority="63" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="48" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="containsText" dxfId="37" priority="51" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A26)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A26)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="containsText" dxfId="35" priority="49" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A27)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A27)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A28">
-    <cfRule type="containsText" dxfId="33" priority="47" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A28)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A28)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A29">
-    <cfRule type="containsText" dxfId="31" priority="45" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="47" priority="61" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A29)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="46" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30">
-    <cfRule type="containsText" dxfId="29" priority="43" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="45" priority="59" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="44" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31">
-    <cfRule type="containsText" dxfId="27" priority="41" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="43" priority="57" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="42" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32">
-    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="41" priority="55" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A32)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="40" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A32)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33">
-    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="39" priority="53" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A33)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="38" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
-    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="37" priority="51" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="36" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A34)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35">
-    <cfRule type="containsText" dxfId="19" priority="31" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A35)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A35)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A36">
-    <cfRule type="containsText" dxfId="17" priority="29" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="35" priority="47" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A36)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="34" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A36)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37">
-    <cfRule type="containsText" dxfId="15" priority="27" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="33" priority="45" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="32" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A37)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38">
-    <cfRule type="containsText" dxfId="13" priority="25" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="31" priority="43" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A38)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="30" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A39:A45">
-    <cfRule type="containsText" dxfId="11" priority="23" operator="containsText" text="&lt;NA&gt;">
+  <conditionalFormatting sqref="A39">
+    <cfRule type="containsText" dxfId="29" priority="41" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="28" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A39)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A46">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A46)))</formula>
+  <conditionalFormatting sqref="A40">
+    <cfRule type="containsText" dxfId="27" priority="39" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A46)))</formula>
+    <cfRule type="containsText" dxfId="26" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A40)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A47">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A47)))</formula>
+  <conditionalFormatting sqref="A41">
+    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A47)))</formula>
+    <cfRule type="containsText" dxfId="24" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A41)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A48">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A48)))</formula>
+  <conditionalFormatting sqref="A42">
+    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A48)))</formula>
+    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A42)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A49">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A49)))</formula>
+  <conditionalFormatting sqref="A43:A49">
+    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A43)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A49)))</formula>
+    <cfRule type="containsText" dxfId="20" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A43)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A51">
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A51)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A51)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A52">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A52)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A52)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A53">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A53)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A53)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A54">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A54)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A54)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A55">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A55)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A50)))</formula>
     </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A50)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A35">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A35)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A35)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A22)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A23)))</formula>
+    </cfRule>
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A50)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2Remote\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV235\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F3D7FE-411D-452D-86BD-1804BA734F74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C99D22F-55BA-4D33-B32A-DDD42002BE46}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="247">
   <si>
     <t>S.No</t>
   </si>
@@ -704,6 +704,69 @@
   </si>
   <si>
     <t>Verify that the supplier import functionality works correctly and valid supplier data is imported successfully</t>
+  </si>
+  <si>
+    <t>Product  Archive</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_02</t>
+  </si>
+  <si>
+    <t>Verify that product is successfully archived and displayed in the Product Archive section.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PA_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PA_02</t>
+  </si>
+  <si>
+    <t>ProductArchive</t>
+  </si>
+  <si>
+    <t>Verify that an archived product is successfully restored and displayed in the Product Listing section.</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_03</t>
+  </si>
+  <si>
+    <t>Verify that archived products are successfully restored using the Bulk Restore option.</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PA_03</t>
+  </si>
+  <si>
+    <t>Size Chart</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SC_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SC_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_SC_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SC_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SC_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_SC_03</t>
+  </si>
+  <si>
+    <t>Verify that a new size chart is successfully created and displayed on the Size Chart Listing page.</t>
+  </si>
+  <si>
+    <t>Verify that the assigned size chart is displayed in the product details of the associated product.</t>
+  </si>
+  <si>
+    <t>Verify that a size chart can be successfully deleted from the Size Chart Listing page.</t>
   </si>
 </sst>
 </file>
@@ -890,7 +953,127 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="88">
+  <dxfs count="100">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2087,7 +2270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -3827,7 +4010,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="16" t="s">
         <v>194</v>
       </c>
@@ -4001,18 +4184,240 @@
         <v>13</v>
       </c>
     </row>
+    <row r="66" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+    </row>
+    <row r="67" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A67" s="13">
+        <v>1</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="E67" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F67" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="I67" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J67" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A68" s="13">
+        <v>2</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D68" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="G68" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H68" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="I68" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J68" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A69" s="13">
+        <v>3</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D69" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="I69" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J69" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+    </row>
+    <row r="71" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A71" s="13">
+        <v>1</v>
+      </c>
+      <c r="B71" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="E71" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A72" s="13">
+        <v>2</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D72" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="E72" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I72" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A73" s="13">
+        <v>3</v>
+      </c>
+      <c r="B73" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="I73" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A28:J28"/>
     <mergeCell ref="A60:J60"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="A47:J47"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A28:J28"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4022,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG55"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -8634,358 +9039,888 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
     </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A56" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+      <c r="U56" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y56" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z56" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A57" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S57" s="3"/>
+      <c r="T57" s="3"/>
+      <c r="U57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="3"/>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="3"/>
+      <c r="AG57" s="3"/>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A58" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y58" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z58" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="3"/>
+      <c r="AC58" s="3"/>
+      <c r="AD58" s="3"/>
+      <c r="AE58" s="3"/>
+      <c r="AF58" s="3"/>
+      <c r="AG58" s="3"/>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A59" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S59" s="3"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA59" s="3"/>
+      <c r="AB59" s="3"/>
+      <c r="AC59" s="3"/>
+      <c r="AD59" s="3"/>
+      <c r="AE59" s="3"/>
+      <c r="AF59" s="3"/>
+      <c r="AG59" s="3"/>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A60" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S60" s="3"/>
+      <c r="T60" s="3"/>
+      <c r="U60" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y60" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z60" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA60" s="3"/>
+      <c r="AB60" s="3"/>
+      <c r="AC60" s="3"/>
+      <c r="AD60" s="3"/>
+      <c r="AE60" s="3"/>
+      <c r="AF60" s="3"/>
+      <c r="AG60" s="3"/>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A61" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y61" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z61" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="87" priority="137" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="99" priority="149" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="138" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="98" priority="150" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="85" priority="111" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="97" priority="123" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="112" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="96" priority="124" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="83" priority="109" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="95" priority="121" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="110" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="94" priority="122" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="81" priority="107" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="93" priority="119" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="108" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="92" priority="120" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="79" priority="105" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="91" priority="117" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="106" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="90" priority="118" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="77" priority="103" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="89" priority="115" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="104" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="88" priority="116" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="75" priority="101" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="87" priority="113" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="102" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="86" priority="114" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="73" priority="99" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="85" priority="111" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="100" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="84" priority="112" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="containsText" dxfId="71" priority="97" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="83" priority="109" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="98" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="82" priority="110" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="containsText" dxfId="69" priority="95" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="81" priority="107" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="96" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="80" priority="108" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="containsText" dxfId="67" priority="93" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="79" priority="105" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="94" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="78" priority="106" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="containsText" dxfId="65" priority="91" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="77" priority="103" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="76" priority="104" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="containsText" dxfId="63" priority="89" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="75" priority="101" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="74" priority="102" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="containsText" dxfId="61" priority="87" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="73" priority="99" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="88" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="72" priority="100" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="containsText" dxfId="59" priority="85" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="71" priority="97" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="86" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="70" priority="98" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="containsText" dxfId="57" priority="83" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="69" priority="95" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="84" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="68" priority="96" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21">
-    <cfRule type="containsText" dxfId="55" priority="81" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="67" priority="93" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="82" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="66" priority="94" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A28">
-    <cfRule type="containsText" dxfId="53" priority="79" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="65" priority="91" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A24)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="80" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="64" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A24)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="51" priority="65" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="63" priority="77" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="62" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="49" priority="63" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="61" priority="75" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="60" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29">
-    <cfRule type="containsText" dxfId="47" priority="61" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="59" priority="73" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A29)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="58" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30">
-    <cfRule type="containsText" dxfId="45" priority="59" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="57" priority="71" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="56" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31">
-    <cfRule type="containsText" dxfId="43" priority="57" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="55" priority="69" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="54" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32">
-    <cfRule type="containsText" dxfId="41" priority="55" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="53" priority="67" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A32)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="52" priority="68" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A32)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33">
-    <cfRule type="containsText" dxfId="39" priority="53" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="51" priority="65" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A33)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="50" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
-    <cfRule type="containsText" dxfId="37" priority="51" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="49" priority="63" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="48" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36">
-    <cfRule type="containsText" dxfId="35" priority="47" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="47" priority="59" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A36)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="46" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A36)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37">
-    <cfRule type="containsText" dxfId="33" priority="45" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="45" priority="57" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="44" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A37)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38">
-    <cfRule type="containsText" dxfId="31" priority="43" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="43" priority="55" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A38)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="42" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39">
-    <cfRule type="containsText" dxfId="29" priority="41" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="41" priority="53" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="40" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
-    <cfRule type="containsText" dxfId="27" priority="39" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="39" priority="51" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="38" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A40)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
-    <cfRule type="containsText" dxfId="25" priority="37" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="37" priority="49" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="36" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42">
-    <cfRule type="containsText" dxfId="23" priority="35" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="35" priority="47" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="34" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A42)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:A49">
-    <cfRule type="containsText" dxfId="21" priority="33" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="33" priority="45" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A43)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="32" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A43)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="31" priority="31" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="30" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A52)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A53)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A53)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A54)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A54)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A50)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A50)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A22)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A23)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A23)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A56">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A56)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A56)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A57">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A57)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A57)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A58">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A58)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A58)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A59:A61">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A59)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A59)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
+++ b/ZlaataQA/src/test/resources/testdata/zltUI/ZltTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarojkumar\git\AdminPanelV235\ZlaataQA\src\test\resources\testdata\zltUI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdul\git\AdminPanelV2Remote\ZlaataQA\src\test\resources\testdata\zltUI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C99D22F-55BA-4D33-B32A-DDD42002BE46}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF66464-F430-4D11-A406-3BC3C9CD663A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{905F911F-FA1A-4DDD-B945-7467E9458D34}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCases-Zlaata" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2266" uniqueCount="268">
   <si>
     <t>S.No</t>
   </si>
@@ -706,67 +706,130 @@
     <t>Verify that the supplier import functionality works correctly and valid supplier data is imported successfully</t>
   </si>
   <si>
-    <t>Product  Archive</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_PA_01</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_PA_02</t>
-  </si>
-  <si>
-    <t>Verify that product is successfully archived and displayed in the Product Archive section.</t>
-  </si>
-  <si>
-    <t>TD_UI_Zlaata_PA_01</t>
-  </si>
-  <si>
-    <t>TD_UI_Zlaata_PA_02</t>
-  </si>
-  <si>
-    <t>ProductArchive</t>
-  </si>
-  <si>
-    <t>Verify that an archived product is successfully restored and displayed in the Product Listing section.</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_PA_03</t>
-  </si>
-  <si>
-    <t>Verify that archived products are successfully restored using the Bulk Restore option.</t>
-  </si>
-  <si>
-    <t>TD_UI_Zlaata_PA_03</t>
-  </si>
-  <si>
-    <t>Size Chart</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_SC_01</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_SC_02</t>
-  </si>
-  <si>
-    <t>TC_UI_Zlaata_SC_03</t>
-  </si>
-  <si>
-    <t>TD_UI_Zlaata_SC_01</t>
-  </si>
-  <si>
-    <t>TD_UI_Zlaata_SC_02</t>
-  </si>
-  <si>
-    <t>TD_UI_Zlaata_SC_03</t>
-  </si>
-  <si>
-    <t>Verify that a new size chart is successfully created and displayed on the Size Chart Listing page.</t>
-  </si>
-  <si>
-    <t>Verify that the assigned size chart is displayed in the product details of the associated product.</t>
-  </si>
-  <si>
-    <t>Verify that a size chart can be successfully deleted from the Size Chart Listing page.</t>
+    <t>Products Module</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PM_01</t>
+  </si>
+  <si>
+    <t>Verify that admin can create a product with valid details and credentials and it is reflected correctly on the Product Listing page</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PM_01</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PM_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PM_02</t>
+  </si>
+  <si>
+    <t>Verify that admin can edit an existing product with all the details and the updated product details are displayed correctly on the Listing and Preview pages</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PM_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PM_03</t>
+  </si>
+  <si>
+    <t>Verify that adjusting product stock from Preview page reflects the correct stock status and details across the application</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PM_04</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PM_04</t>
+  </si>
+  <si>
+    <t>Verify that adding product stock from Preview page reflects the correct stock status and details across the application</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PM_05</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PM_05</t>
+  </si>
+  <si>
+    <t>Verify mandatory field validation when admin saves the Product without entering required details</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PM_06</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PM_06</t>
+  </si>
+  <si>
+    <t>Verify that a partially created Product is displayed as Draft with inactive status on the Product Listing page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PM_07</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_PM_07</t>
+  </si>
+  <si>
+    <t>Verify that admin can add multiple product variants with details through the Inventory Setup module and verify them on the Preview page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_AM_01</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_AM_01</t>
+  </si>
+  <si>
+    <t>Verify that admin can create an accessory with valid details and it is reflected correctly on the Accessories Listing page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_AM_02</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_AM_02</t>
+  </si>
+  <si>
+    <t>Verify that admin can edit an existing accessory and the updated details are reflected correctly on the Accessories Listing page</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_AM_03</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_AM_03</t>
+  </si>
+  <si>
+    <t>Verify that adjusting accessory stock from Preview page reflects the correct stock status and details across the application</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_AM_04</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_AM_04</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Verify that adding accessory stock from Preview page reflects the correct stock status and details across the application</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_AM_05</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_AM_05</t>
+  </si>
+  <si>
+    <t>Verify mandatory field validation when admin saves the accessory without entering required details</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_AM_06</t>
+  </si>
+  <si>
+    <t>TD_UI_Zlaata_AM_06</t>
+  </si>
+  <si>
+    <t>Verify that a partially created accessory is displayed as Draft with inactive status on the Accessories Listing page</t>
   </si>
 </sst>
 </file>
@@ -953,7 +1016,147 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="100">
+  <dxfs count="114">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2270,7 +2473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D1F84-2AD1-4552-9C1F-85B59D75CCFA}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -4010,7 +4213,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="16" t="s">
         <v>194</v>
       </c>
@@ -4184,7 +4387,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="16" t="s">
         <v>226</v>
       </c>
@@ -4209,19 +4412,19 @@
         <v>227</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E67" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I67" s="13" t="s">
         <v>12</v>
@@ -4238,7 +4441,7 @@
         <v>10</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>233</v>
@@ -4247,13 +4450,13 @@
         <v>14</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I68" s="13" t="s">
         <v>12</v>
@@ -4273,19 +4476,19 @@
         <v>234</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I69" s="13" t="s">
         <v>12</v>
@@ -4294,32 +4497,50 @@
         <v>13</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="16" t="s">
+    <row r="70" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A70" s="13">
+        <v>4</v>
+      </c>
+      <c r="B70" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="16"/>
-      <c r="I70" s="16"/>
-      <c r="J70" s="16"/>
+      <c r="D70" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F70" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="G70" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H70" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="I70" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J70" s="13" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="71" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A71" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B71" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E71" s="13" t="s">
         <v>14</v>
@@ -4331,7 +4552,7 @@
         <v>11</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="I71" s="13" t="s">
         <v>12</v>
@@ -4342,13 +4563,13 @@
     </row>
     <row r="72" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A72" s="13">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B72" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D72" s="13" t="s">
         <v>245</v>
@@ -4357,13 +4578,13 @@
         <v>14</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="I72" s="13" t="s">
         <v>12</v>
@@ -4374,28 +4595,28 @@
     </row>
     <row r="73" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A73" s="13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B73" s="13" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E73" s="13" t="s">
         <v>14</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>11</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="I73" s="13" t="s">
         <v>12</v>
@@ -4404,9 +4625,215 @@
         <v>13</v>
       </c>
     </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="16"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+    </row>
+    <row r="75" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A75" s="13">
+        <v>1</v>
+      </c>
+      <c r="B75" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D75" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="I75" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A76" s="13">
+        <v>2</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A77" s="13">
+        <v>3</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="D77" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E77" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="I77" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A78" s="13">
+        <v>4</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D78" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G78" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="I78" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J78" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A79" s="13">
+        <v>5</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>262</v>
+      </c>
+      <c r="D79" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H79" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="I79" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J79" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" s="13" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A80" s="13">
+        <v>6</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="E80" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F80" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="G80" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="H80" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="I80" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J80" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A74:J74"/>
     <mergeCell ref="A66:J66"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A9:J9"/>
@@ -4427,7 +4854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE74813B-34A6-48F5-8B35-1C10409ED694}">
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG68"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="48.88671875" customWidth="1"/>
@@ -9041,7 +9468,7 @@
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>18</v>
@@ -9124,7 +9551,7 @@
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>18</v>
@@ -9207,7 +9634,7 @@
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>18</v>
@@ -9290,7 +9717,7 @@
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>18</v>
@@ -9373,7 +9800,7 @@
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>18</v>
@@ -9456,7 +9883,7 @@
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>18</v>
@@ -9537,390 +9964,1043 @@
       <c r="AF61" s="3"/>
       <c r="AG61" s="3"/>
     </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A62" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S62" s="3"/>
+      <c r="T62" s="3"/>
+      <c r="U62" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y62" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z62" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA62" s="3"/>
+      <c r="AB62" s="3"/>
+      <c r="AC62" s="3"/>
+      <c r="AD62" s="3"/>
+      <c r="AE62" s="3"/>
+      <c r="AF62" s="3"/>
+      <c r="AG62" s="3"/>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A63" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S63" s="3"/>
+      <c r="T63" s="3"/>
+      <c r="U63" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X63" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y63" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z63" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA63" s="3"/>
+      <c r="AB63" s="3"/>
+      <c r="AC63" s="3"/>
+      <c r="AD63" s="3"/>
+      <c r="AE63" s="3"/>
+      <c r="AF63" s="3"/>
+      <c r="AG63" s="3"/>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A64" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S64" s="3"/>
+      <c r="T64" s="3"/>
+      <c r="U64" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y64" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z64" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA64" s="3"/>
+      <c r="AB64" s="3"/>
+      <c r="AC64" s="3"/>
+      <c r="AD64" s="3"/>
+      <c r="AE64" s="3"/>
+      <c r="AF64" s="3"/>
+      <c r="AG64" s="3"/>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A65" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S65" s="3"/>
+      <c r="T65" s="3"/>
+      <c r="U65" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y65" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z65" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA65" s="3"/>
+      <c r="AB65" s="3"/>
+      <c r="AC65" s="3"/>
+      <c r="AD65" s="3"/>
+      <c r="AE65" s="3"/>
+      <c r="AF65" s="3"/>
+      <c r="AG65" s="3"/>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A66" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y66" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z66" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA66" s="3"/>
+      <c r="AB66" s="3"/>
+      <c r="AC66" s="3"/>
+      <c r="AD66" s="3"/>
+      <c r="AE66" s="3"/>
+      <c r="AF66" s="3"/>
+      <c r="AG66" s="3"/>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A67" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y67" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z67" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A68" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S68" s="3"/>
+      <c r="T68" s="3"/>
+      <c r="U68" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="V68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="X68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y68" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z68" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA68" s="3"/>
+      <c r="AB68" s="3"/>
+      <c r="AC68" s="3"/>
+      <c r="AD68" s="3"/>
+      <c r="AE68" s="3"/>
+      <c r="AF68" s="3"/>
+      <c r="AG68" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="containsText" dxfId="99" priority="149" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="113" priority="163" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="98" priority="150" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="112" priority="164" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="containsText" dxfId="97" priority="123" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="111" priority="137" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="96" priority="124" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="110" priority="138" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="containsText" dxfId="95" priority="121" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="109" priority="135" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A9)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="94" priority="122" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="108" priority="136" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="containsText" dxfId="93" priority="119" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="107" priority="133" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A10)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="92" priority="120" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="106" priority="134" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="containsText" dxfId="91" priority="117" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="105" priority="131" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="90" priority="118" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="104" priority="132" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="containsText" dxfId="89" priority="115" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="103" priority="129" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="116" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="102" priority="130" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="containsText" dxfId="87" priority="113" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="101" priority="127" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="86" priority="114" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="100" priority="128" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A12">
-    <cfRule type="containsText" dxfId="85" priority="111" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="99" priority="125" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A12)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="84" priority="112" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="98" priority="126" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A12)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A13">
-    <cfRule type="containsText" dxfId="83" priority="109" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="97" priority="123" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A13)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="110" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="96" priority="124" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A13)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A14">
-    <cfRule type="containsText" dxfId="81" priority="107" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="95" priority="121" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A14)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="108" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="94" priority="122" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A14)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15">
-    <cfRule type="containsText" dxfId="79" priority="105" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="93" priority="119" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A15)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="106" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="92" priority="120" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A15)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16">
-    <cfRule type="containsText" dxfId="77" priority="103" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="91" priority="117" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="76" priority="104" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="90" priority="118" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A17">
-    <cfRule type="containsText" dxfId="75" priority="101" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="89" priority="115" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A17)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="74" priority="102" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="88" priority="116" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A17)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A18">
-    <cfRule type="containsText" dxfId="73" priority="99" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="87" priority="113" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A18)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="72" priority="100" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="86" priority="114" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A18)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19">
-    <cfRule type="containsText" dxfId="71" priority="97" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="85" priority="111" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A19)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="70" priority="98" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="84" priority="112" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A19)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20">
-    <cfRule type="containsText" dxfId="69" priority="95" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="83" priority="109" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A20)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="68" priority="96" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="82" priority="110" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A20)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A21">
-    <cfRule type="containsText" dxfId="67" priority="93" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="81" priority="107" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A21)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="66" priority="94" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="80" priority="108" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A21)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A24:A28">
-    <cfRule type="containsText" dxfId="65" priority="91" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="79" priority="105" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A24)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="78" priority="106" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A24)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="containsText" dxfId="63" priority="77" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="77" priority="91" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="62" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="76" priority="92" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="containsText" dxfId="61" priority="75" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="75" priority="89" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="60" priority="76" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="74" priority="90" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A29">
-    <cfRule type="containsText" dxfId="59" priority="73" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="73" priority="87" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A29)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="58" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="72" priority="88" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A29)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A30">
-    <cfRule type="containsText" dxfId="57" priority="71" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="71" priority="85" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A30)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="70" priority="86" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A30)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A31">
-    <cfRule type="containsText" dxfId="55" priority="69" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="69" priority="83" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A31)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="54" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="68" priority="84" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A31)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A32">
-    <cfRule type="containsText" dxfId="53" priority="67" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="67" priority="81" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A32)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="52" priority="68" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="66" priority="82" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A32)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A33">
-    <cfRule type="containsText" dxfId="51" priority="65" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="65" priority="79" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A33)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="50" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="64" priority="80" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A33)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A34">
-    <cfRule type="containsText" dxfId="49" priority="63" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="63" priority="77" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A34)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="48" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="62" priority="78" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A34)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A36">
-    <cfRule type="containsText" dxfId="47" priority="59" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="61" priority="73" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A36)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="46" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="60" priority="74" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A36)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37">
-    <cfRule type="containsText" dxfId="45" priority="57" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="59" priority="71" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A37)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="44" priority="58" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="58" priority="72" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A37)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38">
-    <cfRule type="containsText" dxfId="43" priority="55" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="57" priority="69" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A38)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="56" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="56" priority="70" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A38)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A39">
-    <cfRule type="containsText" dxfId="41" priority="53" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="55" priority="67" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A39)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="40" priority="54" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="54" priority="68" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A39)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A40">
-    <cfRule type="containsText" dxfId="39" priority="51" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="53" priority="65" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A40)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="38" priority="52" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="52" priority="66" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A40)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
-    <cfRule type="containsText" dxfId="37" priority="49" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="51" priority="63" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A41)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="36" priority="50" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="50" priority="64" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A41)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A42">
-    <cfRule type="containsText" dxfId="35" priority="47" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="49" priority="61" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A42)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="34" priority="48" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="48" priority="62" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A42)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A43:A49">
-    <cfRule type="containsText" dxfId="33" priority="45" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="47" priority="59" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A43)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="46" priority="60" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A43)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A51">
-    <cfRule type="containsText" dxfId="31" priority="31" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="45" priority="45" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A51)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="44" priority="46" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A51)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A52">
-    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="43" priority="43" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A52)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="42" priority="44" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A52)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A53">
-    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="41" priority="41" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A53)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="40" priority="42" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A53)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A54">
-    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="39" priority="39" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A54)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="38" priority="40" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A54)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A55">
-    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="37" priority="37" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A55)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="36" priority="38" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A55)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A50">
-    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="35" priority="35" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A50)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="34" priority="36" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A50)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A35">
-    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="33" priority="33" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A35)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="32" priority="34" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A35)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A11">
-    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="31" priority="31" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="30" priority="32" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A22">
-    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="29" priority="29" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A22)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="28" priority="30" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A22)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23">
-    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="27" priority="27" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A23)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="26" priority="28" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A56">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="25" priority="25" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A56)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="24" priority="26" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A56)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A57">
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+    <cfRule type="containsText" dxfId="23" priority="23" operator="containsText" text="&lt;NA&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A57)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+    <cfRule type="containsText" dxfId="22" priority="24" operator="containsText" text="&lt;EMPTY&gt;">
       <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A57)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A58">
+    <cfRule type="containsText" dxfId="21" priority="21" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A58)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="20" priority="22" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A58)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A59">
+    <cfRule type="containsText" dxfId="19" priority="19" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A59)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="20" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A59)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A60">
+    <cfRule type="containsText" dxfId="17" priority="17" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A60)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="18" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A60)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A61">
+    <cfRule type="containsText" dxfId="15" priority="15" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A61)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A61)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A62">
+    <cfRule type="containsText" dxfId="13" priority="13" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A62)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A62)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A63">
+    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A63)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A63)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A64">
+    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A64)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A64)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A65">
     <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A58)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A65)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A58)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A65)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A59:A61">
+  <conditionalFormatting sqref="A66">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="&lt;NA&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A59)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A66)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="&lt;EMPTY&gt;">
-      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A59)))</formula>
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A66)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A67">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A67)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A67)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A68">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="&lt;NA&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;NA&gt;",A68)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="&lt;EMPTY&gt;">
+      <formula>NOT(ISERROR(SEARCH("&lt;EMPTY&gt;",A68)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
